--- a/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 12,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,61</t>
+          <t>0,0; 16,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 6,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,35</t>
+          <t>1,11; 6,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,45</t>
+          <t>0,92; 4,79</t>
         </is>
       </c>
     </row>
@@ -897,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,35</t>
+          <t>0,0; 13,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,39</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1017,37 +1018,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,42</t>
+          <t>1,13; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,14</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,98</t>
+          <t>0,5; 2,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,65</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3195</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3416</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2925</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3186</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3475</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1180; 7036</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4110</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3488</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4938</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4171</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3020</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1881; 9756</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3108</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3661</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4353</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3993</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4867</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4455</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3215</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4994</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1836; 8510</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>684; 6483</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>605; 5577</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1353; 7870</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>628; 6243</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2576; 10070</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,52</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,86</t>
+          <t>0,0; 17,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,64</t>
+          <t>1,08; 6,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,79</t>
+          <t>0,97; 4,66</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,78</t>
+          <t>0,0; 16,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>0,0; 12,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,83</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,24</t>
+          <t>0,92; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,46; 3,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,31; 2,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,93</t>
+          <t>0,51; 2,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,83; 3,4</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3195</t>
+          <t>0; 3260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2925</t>
+          <t>0; 3427</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3186</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3475</t>
+          <t>0; 2723</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1479,37 +1479,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1180; 7036</t>
+          <t>1143; 7178</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4110</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3488</t>
+          <t>0; 3386</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4938</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 3044</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1881; 9756</t>
+          <t>1982; 9498</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 3753</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1642,17 +1642,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4353</t>
+          <t>0; 4552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3993</t>
+          <t>0; 3839</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4867</t>
+          <t>0; 5567</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4455</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>0; 3598</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1836; 8510</t>
+          <t>1497; 8050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>684; 6483</t>
+          <t>663; 5611</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>605; 5577</t>
+          <t>602; 5531</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1353; 7870</t>
+          <t>1359; 7716</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>628; 6243</t>
+          <t>629; 5706</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2576; 10070</t>
+          <t>2575; 10557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,14 +678,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 16,61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,77</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -693,27 +693,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,56</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,47</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,08; 6,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,35</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,74</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>1,17; 6,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,66</t>
+          <t>0,93; 4,45</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,64</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,53</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,24</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 14,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,63</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,47; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,95</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,92</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,89</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,9; 5,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,87</t>
+          <t>0,51; 2,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,16; 1,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,4</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3365</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3260</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1321,27 +1321,27 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0; 3460</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2809</t>
+          <t>0; 3477</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1368,27 +1368,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3301</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2723</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0; 3054</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3394</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1143; 7178</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3386</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>1237; 6724</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 4773</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3044</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1982; 9498</t>
+          <t>1886; 9066</t>
         </is>
       </c>
     </row>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>767</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>727</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 4078</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 3858</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4622</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4552</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3839</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3660</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5567</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3598</t>
+          <t>0; 4818</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4028</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>673; 5930</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>608; 5694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1497; 8050</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>663; 5611</t>
+          <t>0; 5206</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>602; 5531</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>1461; 8802</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1359; 7716</t>
+          <t>1364; 7995</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>629; 5706</t>
+          <t>624; 6247</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2575; 10557</t>
+          <t>2439; 9734</t>
         </is>
       </c>
     </row>
